--- a/VerveStacks_NOR_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_NOR_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1212582-9A1F-49A4-ADC6-B36EE6ADC992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472D4F04-168A-456E-89CE-03EAB03126BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
